--- a/AtchisonRegime/Outputs/USA/USA_Earnings_Yield/df_regTrendSummaryUSA_Earnings_Yield.xlsx
+++ b/AtchisonRegime/Outputs/USA/USA_Earnings_Yield/df_regTrendSummaryUSA_Earnings_Yield.xlsx
@@ -780,13 +780,13 @@
         <v>45138</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>45747</v>
+        <v>45777</v>
       </c>
       <c r="E16" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4048642891078003</v>
+        <v>0.2853270694157186</v>
       </c>
     </row>
   </sheetData>
